--- a/output/北塩原村_他メンバー素案_網羅性点検.xlsx
+++ b/output/北塩原村_他メンバー素案_網羅性点検.xlsx
@@ -4801,7 +4801,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>既存の村照会M-1〜M-21、県照会Q-1〜Q-8、介護保険側への申し送りK-7・K-8に続けて S 番号を付しました。S-1は修正作業に入る前に必要です。</t>
+          <t>既存の村照会Ｍ-1〜Ｍ-21、県照会Q-1〜Q-8、介護保険側への申し送りK-7・K-8に続けて S 番号を付しました。Ｓ-1は修正作業に入る前に必要です。</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>S-1</t>
+          <t>Ｓ-1</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>S-2</t>
+          <t>Ｓ-2</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>令和8年5月25日の自立支援協議会に提出した「見込量と実績（資料2-3）」の実利用者数（人／月）を計画の実績値としてよいか。よい場合、令和6〜8年度の全サービスの値を受領したい（M-19と同じ）</t>
+          <t>令和8年5月25日の自立支援協議会に提出した「見込量と実績（資料2-3）」の実利用者数（人／月）を計画の実績値としてよいか。よい場合、令和6〜8年度の全サービスの値を受領したい（Ｍ-19と同じ）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -4889,7 +4889,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>S-3</t>
+          <t>Ｓ-3</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -4916,7 +4916,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>S-4</t>
+          <t>Ｓ-4</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -4943,7 +4943,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>S-5</t>
+          <t>Ｓ-5</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -4970,7 +4970,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>S-6</t>
+          <t>Ｓ-6</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -4997,7 +4997,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>S-7</t>
+          <t>Ｓ-7</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -5024,7 +5024,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>S-8</t>
+          <t>Ｓ-8</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -5051,7 +5051,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>S-9</t>
+          <t>Ｓ-9</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -5078,7 +5078,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>S-10</t>
+          <t>Ｓ-10</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
